--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193957</v>
       </c>
       <c r="B2" t="n">
-        <v>92355</v>
+        <v>92357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>137193968</v>
       </c>
       <c r="B3" t="n">
-        <v>80457</v>
+        <v>80460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>137193967</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>137193908</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137193909</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137193910</v>
       </c>
       <c r="B7" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137193956</v>
       </c>
       <c r="B8" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>137193972</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>137193973</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137193958</v>
       </c>
       <c r="B11" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>137193959</v>
       </c>
       <c r="B12" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>137193960</v>
       </c>
       <c r="B13" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>137193961</v>
       </c>
       <c r="B14" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137193962</v>
       </c>
       <c r="B15" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>137193963</v>
       </c>
       <c r="B16" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>137193964</v>
       </c>
       <c r="B17" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>137193965</v>
       </c>
       <c r="B18" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>137193966</v>
       </c>
       <c r="B19" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>137193969</v>
       </c>
       <c r="B51" t="n">
-        <v>80550</v>
+        <v>80553</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193957</v>
       </c>
       <c r="B2" t="n">
-        <v>92357</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>137193968</v>
       </c>
       <c r="B3" t="n">
-        <v>80460</v>
+        <v>80473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>137193967</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>137193908</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137193909</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137193910</v>
       </c>
       <c r="B7" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137193956</v>
       </c>
       <c r="B8" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>137193972</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>137193973</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137193958</v>
       </c>
       <c r="B11" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>137193959</v>
       </c>
       <c r="B12" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>137193960</v>
       </c>
       <c r="B13" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>137193961</v>
       </c>
       <c r="B14" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137193962</v>
       </c>
       <c r="B15" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>137193963</v>
       </c>
       <c r="B16" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>137193964</v>
       </c>
       <c r="B17" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>137193965</v>
       </c>
       <c r="B18" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>137193966</v>
       </c>
       <c r="B19" t="n">
-        <v>80497</v>
+        <v>80510</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137193911</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>137193912</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>137193913</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>137193914</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>137193919</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>137193920</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>137193921</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>137193922</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>137193923</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>137193924</v>
       </c>
       <c r="B29" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>137193925</v>
       </c>
       <c r="B30" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137193927</v>
       </c>
       <c r="B31" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>137193928</v>
       </c>
       <c r="B32" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>137193929</v>
       </c>
       <c r="B33" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>137193930</v>
       </c>
       <c r="B34" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>137193931</v>
       </c>
       <c r="B35" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>137193933</v>
       </c>
       <c r="B36" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>137193934</v>
       </c>
       <c r="B37" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>137193935</v>
       </c>
       <c r="B38" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>137193936</v>
       </c>
       <c r="B39" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>137193937</v>
       </c>
       <c r="B40" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137193938</v>
       </c>
       <c r="B41" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>137193939</v>
       </c>
       <c r="B42" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>137193940</v>
       </c>
       <c r="B43" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>137193941</v>
       </c>
       <c r="B44" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>137193942</v>
       </c>
       <c r="B45" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>137193943</v>
       </c>
       <c r="B46" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>137193945</v>
       </c>
       <c r="B47" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>137193947</v>
       </c>
       <c r="B48" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>137193948</v>
       </c>
       <c r="B49" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>137193949</v>
       </c>
       <c r="B50" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>137193969</v>
       </c>
       <c r="B51" t="n">
-        <v>80553</v>
+        <v>80566</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193957</v>
       </c>
       <c r="B2" t="n">
-        <v>92370</v>
+        <v>92372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>137193968</v>
       </c>
       <c r="B3" t="n">
-        <v>80473</v>
+        <v>80475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         <v>137193967</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>137193908</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137193909</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137193910</v>
       </c>
       <c r="B7" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>137193956</v>
       </c>
       <c r="B8" t="n">
-        <v>92154</v>
+        <v>92156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>137193972</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         <v>137193973</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137193958</v>
       </c>
       <c r="B11" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>137193959</v>
       </c>
       <c r="B12" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>137193960</v>
       </c>
       <c r="B13" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>137193961</v>
       </c>
       <c r="B14" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>137193962</v>
       </c>
       <c r="B15" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>137193963</v>
       </c>
       <c r="B16" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>137193964</v>
       </c>
       <c r="B17" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2778,7 +2778,7 @@
         <v>137193965</v>
       </c>
       <c r="B18" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>137193966</v>
       </c>
       <c r="B19" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
         <v>137193911</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3180,7 +3180,7 @@
         <v>137193912</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>137193913</v>
       </c>
       <c r="B22" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         <v>137193914</v>
       </c>
       <c r="B23" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>137193919</v>
       </c>
       <c r="B24" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
         <v>137193920</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>137193921</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4024,7 +4024,7 @@
         <v>137193922</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>137193923</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>137193924</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         <v>137193925</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>137193927</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         <v>137193928</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>137193929</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>137193930</v>
       </c>
       <c r="B34" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>137193931</v>
       </c>
       <c r="B35" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>137193933</v>
       </c>
       <c r="B36" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>137193934</v>
       </c>
       <c r="B37" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>137193935</v>
       </c>
       <c r="B38" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>137193936</v>
       </c>
       <c r="B39" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>137193937</v>
       </c>
       <c r="B40" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>137193938</v>
       </c>
       <c r="B41" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6091,7 +6091,7 @@
         <v>137193939</v>
       </c>
       <c r="B42" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>137193940</v>
       </c>
       <c r="B43" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>137193941</v>
       </c>
       <c r="B44" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         <v>137193942</v>
       </c>
       <c r="B45" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>137193943</v>
       </c>
       <c r="B46" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>137193945</v>
       </c>
       <c r="B47" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>137193947</v>
       </c>
       <c r="B48" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>137193948</v>
       </c>
       <c r="B49" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>137193949</v>
       </c>
       <c r="B50" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>137193969</v>
       </c>
       <c r="B51" t="n">
-        <v>80566</v>
+        <v>80568</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -710,11 +710,7 @@
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -981,11 +977,7 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1116,11 +1108,7 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1246,11 +1234,7 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1376,11 +1360,7 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1506,11 +1486,7 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -3068,11 +3044,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3208,11 +3180,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3348,11 +3316,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3488,11 +3452,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3628,11 +3588,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3768,11 +3724,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3912,11 +3864,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4052,11 +4000,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -4187,11 +4131,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4329,17 +4269,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4459,11 +4391,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4599,11 +4527,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4739,11 +4663,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4879,11 +4799,7 @@
       <c r="I33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -5019,11 +4935,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -5159,11 +5071,7 @@
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -5294,11 +5202,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -5429,11 +5333,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -5569,11 +5469,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5709,11 +5605,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5844,11 +5736,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5979,11 +5867,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -6119,11 +6003,7 @@
       <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -6259,11 +6139,7 @@
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6399,11 +6275,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6539,11 +6411,7 @@
       <c r="I45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -6679,11 +6547,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -6819,11 +6683,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6954,11 +6814,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -7098,11 +6954,7 @@
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7221,11 +7073,7 @@
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>observerad</t>

--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193957</v>
       </c>
       <c r="B2" t="n">
-        <v>92372</v>
+        <v>92375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137193967</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137193908</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>137193909</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>137193910</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137193956</v>
       </c>
       <c r="B8" t="n">
-        <v>92156</v>
+        <v>92159</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193957</v>
       </c>
       <c r="B2" t="n">
-        <v>92375</v>
+        <v>92385</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193968</v>
       </c>
       <c r="B3" t="n">
-        <v>80475</v>
+        <v>80485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137193967</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137193908</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>137193909</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>137193910</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137193956</v>
       </c>
       <c r="B8" t="n">
-        <v>92159</v>
+        <v>92169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137193972</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137193973</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>137193958</v>
       </c>
       <c r="B11" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137193959</v>
       </c>
       <c r="B12" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>137193960</v>
       </c>
       <c r="B13" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>137193961</v>
       </c>
       <c r="B14" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137193962</v>
       </c>
       <c r="B15" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>137193963</v>
       </c>
       <c r="B16" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>137193964</v>
       </c>
       <c r="B17" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>137193965</v>
       </c>
       <c r="B18" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>137193966</v>
       </c>
       <c r="B19" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>137193911</v>
       </c>
       <c r="B20" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137193912</v>
       </c>
       <c r="B21" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>137193913</v>
       </c>
       <c r="B22" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>137193914</v>
       </c>
       <c r="B23" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>137193919</v>
       </c>
       <c r="B24" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>137193920</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>137193921</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>137193922</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>137193923</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>137193924</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>137193925</v>
       </c>
       <c r="B30" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>137193927</v>
       </c>
       <c r="B31" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>137193928</v>
       </c>
       <c r="B32" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>137193929</v>
       </c>
       <c r="B33" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>137193930</v>
       </c>
       <c r="B34" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>137193931</v>
       </c>
       <c r="B35" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>137193933</v>
       </c>
       <c r="B36" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137193934</v>
       </c>
       <c r="B37" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137193935</v>
       </c>
       <c r="B38" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>137193936</v>
       </c>
       <c r="B39" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>137193937</v>
       </c>
       <c r="B40" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137193938</v>
       </c>
       <c r="B41" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>137193939</v>
       </c>
       <c r="B42" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>137193940</v>
       </c>
       <c r="B43" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>137193941</v>
       </c>
       <c r="B44" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>137193942</v>
       </c>
       <c r="B45" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>137193943</v>
       </c>
       <c r="B46" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>137193945</v>
       </c>
       <c r="B47" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>137193947</v>
       </c>
       <c r="B48" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>137193948</v>
       </c>
       <c r="B49" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>137193949</v>
       </c>
       <c r="B50" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>137193969</v>
       </c>
       <c r="B51" t="n">
-        <v>80568</v>
+        <v>80578</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193957</v>
       </c>
       <c r="B2" t="n">
-        <v>92385</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137193967</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137193908</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>137193909</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>137193910</v>
       </c>
       <c r="B7" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137193956</v>
       </c>
       <c r="B8" t="n">
-        <v>92169</v>
+        <v>92170</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193957</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193968</v>
       </c>
       <c r="B3" t="n">
-        <v>80485</v>
+        <v>80488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137193967</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137193908</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>137193909</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>137193910</v>
       </c>
       <c r="B7" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137193956</v>
       </c>
       <c r="B8" t="n">
-        <v>92170</v>
+        <v>92173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137193972</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137193973</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>137193958</v>
       </c>
       <c r="B11" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137193959</v>
       </c>
       <c r="B12" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>137193960</v>
       </c>
       <c r="B13" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>137193961</v>
       </c>
       <c r="B14" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137193962</v>
       </c>
       <c r="B15" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>137193963</v>
       </c>
       <c r="B16" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>137193964</v>
       </c>
       <c r="B17" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>137193965</v>
       </c>
       <c r="B18" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>137193966</v>
       </c>
       <c r="B19" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>137193911</v>
       </c>
       <c r="B20" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137193912</v>
       </c>
       <c r="B21" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>137193913</v>
       </c>
       <c r="B22" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>137193914</v>
       </c>
       <c r="B23" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>137193919</v>
       </c>
       <c r="B24" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>137193920</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>137193921</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>137193922</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>137193923</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>137193924</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>137193925</v>
       </c>
       <c r="B30" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>137193927</v>
       </c>
       <c r="B31" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>137193928</v>
       </c>
       <c r="B32" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>137193929</v>
       </c>
       <c r="B33" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>137193930</v>
       </c>
       <c r="B34" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>137193931</v>
       </c>
       <c r="B35" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>137193933</v>
       </c>
       <c r="B36" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137193934</v>
       </c>
       <c r="B37" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137193935</v>
       </c>
       <c r="B38" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>137193936</v>
       </c>
       <c r="B39" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>137193937</v>
       </c>
       <c r="B40" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137193938</v>
       </c>
       <c r="B41" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>137193939</v>
       </c>
       <c r="B42" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>137193940</v>
       </c>
       <c r="B43" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>137193941</v>
       </c>
       <c r="B44" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>137193942</v>
       </c>
       <c r="B45" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>137193943</v>
       </c>
       <c r="B46" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>137193945</v>
       </c>
       <c r="B47" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>137193947</v>
       </c>
       <c r="B48" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>137193948</v>
       </c>
       <c r="B49" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>137193949</v>
       </c>
       <c r="B50" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>137193969</v>
       </c>
       <c r="B51" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193957</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137193967</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137193908</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>137193909</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>137193910</v>
       </c>
       <c r="B7" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137193956</v>
       </c>
       <c r="B8" t="n">
-        <v>92173</v>
+        <v>92175</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193957</v>
       </c>
       <c r="B2" t="n">
-        <v>92391</v>
+        <v>92396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193968</v>
       </c>
       <c r="B3" t="n">
-        <v>80488</v>
+        <v>80493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137193967</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137193908</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>137193909</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>137193910</v>
       </c>
       <c r="B7" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137193956</v>
       </c>
       <c r="B8" t="n">
-        <v>92175</v>
+        <v>92180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137193972</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137193973</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>137193958</v>
       </c>
       <c r="B11" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137193959</v>
       </c>
       <c r="B12" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>137193960</v>
       </c>
       <c r="B13" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>137193961</v>
       </c>
       <c r="B14" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137193962</v>
       </c>
       <c r="B15" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>137193963</v>
       </c>
       <c r="B16" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>137193964</v>
       </c>
       <c r="B17" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>137193965</v>
       </c>
       <c r="B18" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>137193966</v>
       </c>
       <c r="B19" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
         <v>137193911</v>
       </c>
       <c r="B20" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>137193912</v>
       </c>
       <c r="B21" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         <v>137193913</v>
       </c>
       <c r="B22" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>137193914</v>
       </c>
       <c r="B23" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3560,7 +3560,7 @@
         <v>137193919</v>
       </c>
       <c r="B24" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3696,7 +3696,7 @@
         <v>137193920</v>
       </c>
       <c r="B25" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3836,7 +3836,7 @@
         <v>137193921</v>
       </c>
       <c r="B26" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>137193922</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>137193923</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>137193924</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>137193925</v>
       </c>
       <c r="B30" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4499,7 +4499,7 @@
         <v>137193927</v>
       </c>
       <c r="B31" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>137193928</v>
       </c>
       <c r="B32" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
         <v>137193929</v>
       </c>
       <c r="B33" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>137193930</v>
       </c>
       <c r="B34" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>137193931</v>
       </c>
       <c r="B35" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>137193933</v>
       </c>
       <c r="B36" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>137193934</v>
       </c>
       <c r="B37" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>137193935</v>
       </c>
       <c r="B38" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         <v>137193936</v>
       </c>
       <c r="B39" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>137193937</v>
       </c>
       <c r="B40" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>137193938</v>
       </c>
       <c r="B41" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
         <v>137193939</v>
       </c>
       <c r="B42" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>137193940</v>
       </c>
       <c r="B43" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>137193941</v>
       </c>
       <c r="B44" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
         <v>137193942</v>
       </c>
       <c r="B45" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>137193943</v>
       </c>
       <c r="B46" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>137193945</v>
       </c>
       <c r="B47" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>137193947</v>
       </c>
       <c r="B48" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6922,7 +6922,7 @@
         <v>137193948</v>
       </c>
       <c r="B49" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>137193949</v>
       </c>
       <c r="B50" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>137193969</v>
       </c>
       <c r="B51" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193957</v>
       </c>
       <c r="B2" t="n">
-        <v>92396</v>
+        <v>92408</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193968</v>
       </c>
       <c r="B3" t="n">
-        <v>80493</v>
+        <v>80504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137193967</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137193908</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>137193909</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>137193910</v>
       </c>
       <c r="B7" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137193956</v>
       </c>
       <c r="B8" t="n">
-        <v>92180</v>
+        <v>92192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137193972</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137193973</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>137193958</v>
       </c>
       <c r="B11" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137193959</v>
       </c>
       <c r="B12" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>137193960</v>
       </c>
       <c r="B13" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>137193961</v>
       </c>
       <c r="B14" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137193962</v>
       </c>
       <c r="B15" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>137193963</v>
       </c>
       <c r="B16" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>137193964</v>
       </c>
       <c r="B17" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>137193965</v>
       </c>
       <c r="B18" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>137193966</v>
       </c>
       <c r="B19" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>137193969</v>
       </c>
       <c r="B51" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193957</v>
       </c>
       <c r="B2" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193968</v>
       </c>
       <c r="B3" t="n">
-        <v>80504</v>
+        <v>80505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137193967</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137193908</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>137193909</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>137193910</v>
       </c>
       <c r="B7" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137193956</v>
       </c>
       <c r="B8" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137193972</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137193973</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>137193958</v>
       </c>
       <c r="B11" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137193959</v>
       </c>
       <c r="B12" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>137193960</v>
       </c>
       <c r="B13" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>137193961</v>
       </c>
       <c r="B14" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137193962</v>
       </c>
       <c r="B15" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>137193963</v>
       </c>
       <c r="B16" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>137193964</v>
       </c>
       <c r="B17" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>137193965</v>
       </c>
       <c r="B18" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>137193966</v>
       </c>
       <c r="B19" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>137193969</v>
       </c>
       <c r="B51" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 40326-2026 artfynd.xlsx
+++ b/artfynd/A 40326-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193957</v>
       </c>
       <c r="B2" t="n">
-        <v>92409</v>
+        <v>92412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>137193968</v>
       </c>
       <c r="B3" t="n">
-        <v>80505</v>
+        <v>80507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>137193967</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>137193908</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>137193909</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v>137193910</v>
       </c>
       <c r="B7" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>137193956</v>
       </c>
       <c r="B8" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>137193972</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>137193973</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>137193958</v>
       </c>
       <c r="B11" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>137193959</v>
       </c>
       <c r="B12" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
         <v>137193960</v>
       </c>
       <c r="B13" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>137193961</v>
       </c>
       <c r="B14" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>137193962</v>
       </c>
       <c r="B15" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>137193963</v>
       </c>
       <c r="B16" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>137193964</v>
       </c>
       <c r="B17" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>137193965</v>
       </c>
       <c r="B18" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>137193966</v>
       </c>
       <c r="B19" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>137193969</v>
       </c>
       <c r="B51" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
